--- a/src/test/fixtures/forms-responses-http/multi-export-en.xlsx
+++ b/src/test/fixtures/forms-responses-http/multi-export-en.xlsx
@@ -36,7 +36,7 @@
     <x:t>Historical risks</x:t>
   </x:si>
   <x:si>
-    <x:t>T8EE7F363-000001</x:t>
+    <x:t>T2757609E-000001</x:t>
   </x:si>
   <x:si>
     <x:t>Unavailable</x:t>
@@ -48,7 +48,7 @@
     <x:t>Historical noise; Historical cold</x:t>
   </x:si>
   <x:si>
-    <x:t>T8EE7F363-000002</x:t>
+    <x:t>T2757609E-000002</x:t>
   </x:si>
   <x:si>
     <x:t>Cold</x:t>
@@ -57,10 +57,10 @@
     <x:t>Historical cold</x:t>
   </x:si>
   <x:si>
-    <x:t>T8EE7F363-000003</x:t>
-  </x:si>
-  <x:si>
-    <x:t>T8EE7F363-000004</x:t>
+    <x:t>T2757609E-000003</x:t>
+  </x:si>
+  <x:si>
+    <x:t>T2757609E-000004</x:t>
   </x:si>
 </x:sst>
 </file>

--- a/src/test/fixtures/forms-responses-http/multi-export-en.xlsx
+++ b/src/test/fixtures/forms-responses-http/multi-export-en.xlsx
@@ -36,7 +36,7 @@
     <x:t>Historical risks</x:t>
   </x:si>
   <x:si>
-    <x:t>T2757609E-000001</x:t>
+    <x:t>T76559C58-000001</x:t>
   </x:si>
   <x:si>
     <x:t>Unavailable</x:t>
@@ -48,7 +48,7 @@
     <x:t>Historical noise; Historical cold</x:t>
   </x:si>
   <x:si>
-    <x:t>T2757609E-000002</x:t>
+    <x:t>T76559C58-000002</x:t>
   </x:si>
   <x:si>
     <x:t>Cold</x:t>
@@ -57,10 +57,10 @@
     <x:t>Historical cold</x:t>
   </x:si>
   <x:si>
-    <x:t>T2757609E-000003</x:t>
-  </x:si>
-  <x:si>
-    <x:t>T2757609E-000004</x:t>
+    <x:t>T76559C58-000003</x:t>
+  </x:si>
+  <x:si>
+    <x:t>T76559C58-000004</x:t>
   </x:si>
 </x:sst>
 </file>

--- a/src/test/fixtures/forms-responses-http/multi-export-en.xlsx
+++ b/src/test/fixtures/forms-responses-http/multi-export-en.xlsx
@@ -36,7 +36,7 @@
     <x:t>Historical risks</x:t>
   </x:si>
   <x:si>
-    <x:t>T76559C58-000001</x:t>
+    <x:t>T30510478-000001</x:t>
   </x:si>
   <x:si>
     <x:t>Unavailable</x:t>
@@ -48,7 +48,7 @@
     <x:t>Historical noise; Historical cold</x:t>
   </x:si>
   <x:si>
-    <x:t>T76559C58-000002</x:t>
+    <x:t>T30510478-000002</x:t>
   </x:si>
   <x:si>
     <x:t>Cold</x:t>
@@ -57,10 +57,10 @@
     <x:t>Historical cold</x:t>
   </x:si>
   <x:si>
-    <x:t>T76559C58-000003</x:t>
-  </x:si>
-  <x:si>
-    <x:t>T76559C58-000004</x:t>
+    <x:t>T30510478-000003</x:t>
+  </x:si>
+  <x:si>
+    <x:t>T30510478-000004</x:t>
   </x:si>
 </x:sst>
 </file>
